--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.37976872936511</v>
+        <v>7.699212418521831</v>
       </c>
       <c r="D2" t="n">
-        <v>29.15169169857709</v>
+        <v>4.737149901018777</v>
       </c>
       <c r="E2" t="n">
-        <v>10.39748575132544</v>
+        <v>1.689591434590384</v>
       </c>
       <c r="F2" t="n">
-        <v>5.956753471352511</v>
+        <v>0.967972439094783</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.04761627920076</v>
+        <v>6.995237645370124</v>
       </c>
       <c r="D3" t="n">
-        <v>14.35315743875552</v>
+        <v>2.332388083797772</v>
       </c>
       <c r="E3" t="n">
-        <v>10.39748575132544</v>
+        <v>1.689591434590384</v>
       </c>
       <c r="F3" t="n">
-        <v>5.956753471352511</v>
+        <v>0.967972439094783</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.84743686617101</v>
+        <v>3.87520849075279</v>
       </c>
       <c r="D4" t="n">
-        <v>20.88156400596396</v>
+        <v>3.393254150969143</v>
       </c>
       <c r="E4" t="n">
-        <v>10.39748575132544</v>
+        <v>1.689591434590384</v>
       </c>
       <c r="F4" t="n">
-        <v>5.956753471352511</v>
+        <v>0.967972439094783</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.51106778495844</v>
+        <v>4.145548515055746</v>
       </c>
       <c r="D5" t="n">
-        <v>14.93754415795911</v>
+        <v>2.427350925668355</v>
       </c>
       <c r="E5" t="n">
-        <v>10.39748575132544</v>
+        <v>1.689591434590384</v>
       </c>
       <c r="F5" t="n">
-        <v>5.956753471352511</v>
+        <v>0.967972439094783</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
